--- a/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
+++ b/InputData/fuels/PEIIR/Pollutant Emissions Intensity Improvement Rate.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23628"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\fuels\PEIIR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\fuels\PEIIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C5BDB8-164C-4260-8BDD-310BFE54C72D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="135" windowWidth="19425" windowHeight="10740" tabRatio="783"/>
+    <workbookView xWindow="21045" yWindow="1410" windowWidth="33360" windowHeight="21225" tabRatio="783" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -21,14 +22,7 @@
     <sheet name="PEIIR-TFPEIIR-motorbikes" sheetId="13" r:id="rId7"/>
     <sheet name="PEIIR-EFPEIIR" sheetId="6" r:id="rId8"/>
     <sheet name="PEIIR-BFPEIIR" sheetId="7" r:id="rId9"/>
-    <sheet name="PEIIR-IFPEIIR-cement" sheetId="19" r:id="rId10"/>
-    <sheet name="PEIIR-IFPEIIR-ngps" sheetId="20" r:id="rId11"/>
-    <sheet name="PEIIR-IFPEIIR-steel" sheetId="24" r:id="rId12"/>
-    <sheet name="PEIIR-IFPEIIR-chemicals" sheetId="21" r:id="rId13"/>
-    <sheet name="PEIIR-IFPEIIR-mining" sheetId="22" r:id="rId14"/>
-    <sheet name="PEIIR-IFPEIIR-waste-mgmt" sheetId="25" r:id="rId15"/>
-    <sheet name="PEIIR-IFPEIIR-agriculture" sheetId="23" r:id="rId16"/>
-    <sheet name="PEIIR-IFPEIIR-other-industries" sheetId="26" r:id="rId17"/>
+    <sheet name="PEIIR-IFPEIIR" sheetId="19" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="BTU_per_kWh">About!#REF!</definedName>
@@ -40,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="66">
   <si>
     <t>Source:</t>
   </si>
@@ -266,7 +260,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -363,8 +357,8 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 21" xfId="1"/>
-    <cellStyle name="Normal 40" xfId="2"/>
+    <cellStyle name="Normal 21" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 40" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -460,6 +454,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -495,6 +506,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -670,35 +698,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.73046875" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
     <col min="2" max="2" width="73" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,97 +734,97 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>54</v>
       </c>
@@ -808,25 +836,25 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>65</v>
       </c>
@@ -861,7 +889,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -896,7 +924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -931,7 +959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -966,7 +994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1001,7 +1029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1036,7 +1064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1071,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1106,7 +1134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1141,7 +1169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1176,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1211,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1246,3367 +1274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="3"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="13.3984375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.73046875" customWidth="1"/>
-    <col min="5" max="5" width="14.1328125" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="15.265625" customWidth="1"/>
-    <col min="10" max="10" width="13.59765625" customWidth="1"/>
-    <col min="11" max="11" width="11.59765625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -4648,26 +1316,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>65</v>
       </c>
@@ -4702,7 +1370,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -4737,7 +1405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -4772,7 +1440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -4807,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4842,7 +1510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -4877,7 +1545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4912,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -4947,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -4982,7 +1650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5017,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5052,7 +1720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5087,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5129,26 +1797,26 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
-    <col min="3" max="3" width="14.265625" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>65</v>
       </c>
@@ -5183,7 +1851,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -5218,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5253,7 +1921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5288,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5323,7 +1991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5358,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5393,7 +2061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5428,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5463,7 +2131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5498,7 +2166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -5533,7 +2201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -5568,7 +2236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5610,26 +2278,26 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
-    <col min="3" max="3" width="12.86328125" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="14.59765625" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>65</v>
       </c>
@@ -5664,7 +2332,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -5699,7 +2367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -5734,7 +2402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5769,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -5804,7 +2472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -5839,7 +2507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -5874,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -5909,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -5944,7 +2612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -5979,7 +2647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6014,7 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6049,7 +2717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -6091,26 +2759,26 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>65</v>
       </c>
@@ -6145,7 +2813,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -6180,7 +2848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6215,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6250,7 +2918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6285,7 +2953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6320,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -6355,7 +3023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6390,7 +3058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6425,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6460,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6495,7 +3163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6530,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -6572,26 +3240,26 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>65</v>
       </c>
@@ -6626,7 +3294,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -6661,7 +3329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -6696,7 +3364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6731,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -6766,7 +3434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6801,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -6836,7 +3504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6871,7 +3539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6906,7 +3574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6941,7 +3609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6976,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -7011,7 +3679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -7053,26 +3721,26 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.265625" customWidth="1"/>
-    <col min="3" max="3" width="13.265625" customWidth="1"/>
-    <col min="4" max="4" width="21.3984375" customWidth="1"/>
-    <col min="5" max="5" width="18.59765625" customWidth="1"/>
-    <col min="6" max="6" width="18.265625" customWidth="1"/>
-    <col min="7" max="7" width="16.59765625" customWidth="1"/>
-    <col min="8" max="8" width="11.1328125" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" customWidth="1"/>
-    <col min="10" max="10" width="13.1328125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>65</v>
       </c>
@@ -7107,7 +3775,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -7142,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7177,7 +3845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -7212,7 +3880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -7247,7 +3915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7282,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7317,7 +3985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -7352,7 +4020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -7387,7 +4055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -7422,7 +4090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -7457,7 +4125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -7492,7 +4160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -7534,30 +4202,30 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="5" max="5" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.265625" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="12.73046875" customWidth="1"/>
-    <col min="10" max="10" width="15.73046875" customWidth="1"/>
-    <col min="11" max="11" width="16.1328125" customWidth="1"/>
-    <col min="12" max="12" width="20.73046875" customWidth="1"/>
-    <col min="13" max="13" width="13.73046875" customWidth="1"/>
-    <col min="14" max="14" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1328125" customWidth="1"/>
-    <col min="16" max="16" width="17.1328125" customWidth="1"/>
-    <col min="17" max="17" width="15.59765625" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="5" customFormat="1" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>65</v>
       </c>
@@ -7610,7 +4278,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -7663,7 +4331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7716,7 +4384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -7769,7 +4437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -7822,7 +4490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7875,7 +4543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -7928,7 +4596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -7981,7 +4649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -8034,7 +4702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -8087,7 +4755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -8140,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -8193,7 +4861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -8253,25 +4921,25 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.1328125" customWidth="1"/>
-    <col min="3" max="3" width="16.73046875" customWidth="1"/>
-    <col min="4" max="4" width="16.86328125" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="7" max="7" width="14.73046875" customWidth="1"/>
-    <col min="8" max="8" width="13.265625" customWidth="1"/>
-    <col min="9" max="9" width="24.73046875" customWidth="1"/>
-    <col min="10" max="10" width="22.86328125" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>65</v>
       </c>
@@ -8306,7 +4974,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -8341,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8376,7 +5044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -8411,7 +5079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8446,7 +5114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8481,7 +5149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -8516,7 +5184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -8551,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -8586,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -8621,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -8656,7 +5324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -8691,7 +5359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -8733,31 +5401,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -8765,24 +5434,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -8801,70 +5531,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -8975,23 +5658,10 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4E4D60E-CBE4-47D2-9693-9B20AAF594C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06F8FB9F-AAB2-48C9-9913-ED6BBE1CF976}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB1570B4-24C8-46CF-9BAB-BD3A8AD7051A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E4AEB64-ACB4-4D87-94DB-033F826A563F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09A39533-C54F-473A-B426-19669C01DF2D}"/>
 </file>